--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261012.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20261012.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>845,349</t>
+          <t>143,921</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>143,921</t>
+          <t>845,349</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>384,000</t>
+          <t>2,561,703</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>2,561,703</t>
+          <t>384,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>44,000</t>
+          <t>143,386</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>143,386</t>
+          <t>44,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>224,000</t>
+          <t>1,169,076</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,169,076</t>
+          <t>224,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>315,000</t>
+          <t>286,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>286,000</t>
+          <t>315,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>748,000</t>
+          <t>4,891,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>4,891,956</t>
+          <t>748,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>1,733,000</t>
+          <t>327,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>63,538</t>
+          <t>1,733,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>晶豪科</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>409,000</t>
+          <t>63,538</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>晶豪科</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>327,000</t>
+          <t>409,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>175,000</t>
+          <t>251,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>175,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>670,000</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>251,000</t>
+          <t>670,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
